--- a/AAII_Financials/Quarterly/TRV_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TRV_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="92">
   <si>
     <t>TRV</t>
   </si>
@@ -656,515 +656,527 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="42" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>12153000</v>
+      </c>
+      <c r="E8" s="3">
         <v>11924000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>12432000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>12470000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>12116000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>11810000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>12008000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>11904000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>11283000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>11228000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>10927000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>10635000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>10098000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>9704000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>9639000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>9317000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>9156000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>8810000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>9012000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>8806000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>8687000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>8313000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>8434000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>8271000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>7407000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>7924000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>8065000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>8013000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>7835000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>7672000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>7796000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>7723000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>7478000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>7286000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>7453000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>7330000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>7189000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>6944000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>7196000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>6965000</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>7708000</v>
+      </c>
+      <c r="E9" s="3">
         <v>8148000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>7669000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>8443000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>8591000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>9784000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>7841000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>8786000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>9051000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>8354000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>7521000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>8753000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>8746000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>7421000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1434000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1406000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1365000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1310000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1301000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1281000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1254000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1207000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1215000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1207000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1173000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1178000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1181000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1169000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1134000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1117000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1122000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1117000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1081000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1061000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1072000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1059000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>1032000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>1003000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>1013000</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>1012000</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>4445000</v>
+      </c>
+      <c r="E10" s="3">
         <v>3776000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4763000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>4027000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3525000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2026000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>4167000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3118000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2232000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2874000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>3406000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1882000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1352000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2283000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>8205000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>7911000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>7791000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>7500000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>7711000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>7525000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>7433000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>7106000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>7219000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>7064000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>6234000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>6746000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>6884000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>6844000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>6701000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>6555000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>6674000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>6606000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>6397000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>6225000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>6381000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>6271000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>6157000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>5941000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>6183000</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>5953000</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1207,8 +1219,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1329,8 +1342,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1451,8 +1467,11 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1495,17 +1514,17 @@
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>5000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>20000</v>
-      </c>
-      <c r="T14" s="3">
-        <v>1000</v>
       </c>
       <c r="U14" s="3">
         <v>1000</v>
@@ -1514,112 +1533,115 @@
         <v>1000</v>
       </c>
       <c r="W14" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
       </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>37000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>6000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>16000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>2000</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
       <c r="AE14" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF14" s="3">
         <v>1000</v>
       </c>
       <c r="AG14" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH14" s="3">
         <v>0</v>
       </c>
       <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ14" s="3">
-        <v>0</v>
-      </c>
       <c r="AK14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="3">
         <v>2000</v>
-      </c>
-      <c r="AL14" s="3">
-        <v>5000</v>
       </c>
       <c r="AM14" s="3">
         <v>5000</v>
       </c>
       <c r="AN14" s="3">
+        <v>5000</v>
+      </c>
+      <c r="AO14" s="3">
         <v>2000</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>3000</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>170000</v>
+      </c>
+      <c r="E15" s="3">
         <v>193000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>162000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>166000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>164000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>188000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>163000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>174000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>182000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>196000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>170000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>169000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>179000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>204000</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1695,8 +1717,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1736,252 +1761,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>9273000</v>
+      </c>
+      <c r="E17" s="3">
         <v>9689000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>9213000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>10015000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>10136000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>11243000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>9316000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>10246000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>10529000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>9760000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>8810000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>10065000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>10054000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>8688000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>8561000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>8692000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>8411000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>7541000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>7274000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>7933000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>7473000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>7340000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>6735000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>7198000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>7407000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>7120000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>6908000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>7497000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>7081000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>6617000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>6963000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>6831000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>6757000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>6419000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>6500000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>6915000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>6307000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>6095000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>5804000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>5929000</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2880000</v>
+      </c>
+      <c r="E18" s="3">
         <v>2235000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3219000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2455000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1980000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>567000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2692000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1658000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>754000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1468000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2117000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>570000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>44000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1016000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1078000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>625000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>745000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1269000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1738000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>873000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1214000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>973000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1699000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1073000</v>
       </c>
-      <c r="AA18" s="3">
-        <v>0</v>
-      </c>
       <c r="AB18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="3">
         <v>804000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1157000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>516000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>754000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1055000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>833000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>892000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>721000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>867000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>953000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>415000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>882000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>849000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>1392000</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>1036000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2024,8 +2056,9 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2068,15 +2101,15 @@
       <c r="P20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R20" s="3">
         <v>-3000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-9000</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
         <v>0</v>
       </c>
@@ -2146,150 +2179,156 @@
       <c r="AP20" s="3">
         <v>0</v>
       </c>
+      <c r="AQ20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>3050000</v>
+      </c>
+      <c r="E21" s="3">
         <v>2428000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>3381000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2621000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2144000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>755000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2855000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1832000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>936000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1664000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2287000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>739000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>223000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1220000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2696000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2217000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2320000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2813000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>3247000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2366000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2683000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2415000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>3126000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>2466000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1361000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>2185000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>2520000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1865000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>2078000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>2383000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>2149000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>2207000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>2001000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>2140000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>2227000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1676000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>2112000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>2063000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>2607000</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>2259000</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>116000</v>
+        <v>113000</v>
       </c>
       <c r="E22" s="3">
         <v>116000</v>
       </c>
       <c r="F22" s="3">
+        <v>116000</v>
+      </c>
+      <c r="G22" s="3">
         <v>111000</v>
-      </c>
-      <c r="G22" s="3">
-        <v>99000</v>
       </c>
       <c r="H22" s="3">
         <v>99000</v>
       </c>
       <c r="I22" s="3">
-        <v>98000</v>
+        <v>99000</v>
       </c>
       <c r="J22" s="3">
         <v>98000</v>
@@ -2307,10 +2346,10 @@
         <v>98000</v>
       </c>
       <c r="O22" s="3">
+        <v>98000</v>
+      </c>
+      <c r="P22" s="3">
         <v>92000</v>
-      </c>
-      <c r="P22" s="3">
-        <v>88000</v>
       </c>
       <c r="Q22" s="3">
         <v>88000</v>
@@ -2322,320 +2361,329 @@
         <v>88000</v>
       </c>
       <c r="T22" s="3">
+        <v>88000</v>
+      </c>
+      <c r="U22" s="3">
         <v>87000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>88000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>87000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>83000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>82000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>83000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>87000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>85000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>84000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>83000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>84000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>89000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>88000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>87000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>86000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>90000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>89000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>93000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>95000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>92000</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>89000</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>90000</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>89000</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2767000</v>
+      </c>
+      <c r="E23" s="3">
         <v>2119000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3103000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2344000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1881000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>468000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2594000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1560000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>656000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1370000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2019000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>472000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-48000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>928000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>987000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>528000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>657000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1182000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1650000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>786000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1131000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>891000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1616000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>986000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-85000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>720000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1074000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>432000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>665000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>967000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>746000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>806000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>631000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>778000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>860000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>320000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>790000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>760000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>1302000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>947000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>559000</v>
+      </c>
+      <c r="E24" s="3">
         <v>408000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>607000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>456000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>372000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>73000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>512000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>300000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>122000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>247000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>393000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>68000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-34000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-47000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>168000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>74000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>106000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>164000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>317000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>124000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>197000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>158000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>306000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>159000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-45000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>120000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>201000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>36000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>108000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>171000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>125000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>97000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>107000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>109000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>180000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>27000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>195000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>143000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>359000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>231000</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2756,252 +2804,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2208000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1711000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2496000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1888000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1509000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>395000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2082000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1260000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>534000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1123000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1626000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>404000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-14000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>975000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>819000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>454000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>551000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1018000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1333000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>662000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>934000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>733000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1310000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>827000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-40000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>600000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>873000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>396000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>557000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>796000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>621000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>709000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>524000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>669000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>680000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>293000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>595000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>617000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>943000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>716000</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2193000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1699000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2477000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1875000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1498000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>392000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2066000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1250000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>529000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1115000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1614000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>401000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-15000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>968000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>814000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>450000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>547000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1011000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1323000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>657000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>927000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>728000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1300000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>821000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-41000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>595000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>866000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>393000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>553000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>791000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>616000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>704000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>520000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>664000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>676000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>291000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>590000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>613000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>937000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>710000</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3122,8 +3179,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3208,17 +3268,17 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
+      <c r="AE29" s="3">
+        <v>0</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH29" s="3" t="s">
-        <v>8</v>
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3">
+        <v>0</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>8</v>
@@ -3226,12 +3286,12 @@
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL29" s="3">
         <v>-129000</v>
       </c>
-      <c r="AL29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AM29" s="3" t="s">
         <v>8</v>
       </c>
@@ -3244,8 +3304,11 @@
       <c r="AP29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3366,8 +3429,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3488,8 +3554,11 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3532,15 +3601,15 @@
       <c r="P32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R32" s="3">
         <v>3000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>9000</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
         <v>0</v>
       </c>
@@ -3610,130 +3679,136 @@
       <c r="AP32" s="3">
         <v>0</v>
       </c>
+      <c r="AQ32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2208000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1711000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2496000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1888000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1509000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>395000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2082000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1260000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>534000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1123000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1626000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>404000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-14000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>975000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>814000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>450000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>547000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1011000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1323000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>657000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>927000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>728000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1300000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>821000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-41000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>595000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>866000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>393000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>553000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>791000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>616000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>704000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>520000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>664000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>547000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>291000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>590000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>613000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>937000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>710000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3854,257 +3929,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2208000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1711000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2496000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1888000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1509000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>395000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2082000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1260000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>534000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1123000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1626000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>404000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-14000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>975000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>814000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>450000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>547000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1011000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1323000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>657000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>927000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>728000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1300000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>821000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-41000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>595000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>866000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>393000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>553000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>791000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>616000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>704000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>520000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>664000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>547000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>291000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>590000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>613000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>937000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>710000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4147,8 +4231,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4191,175 +4276,179 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>482000</v>
+      </c>
+      <c r="E41" s="3">
         <v>481000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>710000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>592000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>521000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>586000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>568000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>772000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>729000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>667000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>650000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>593000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>605000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>767000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>799000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>773000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>710000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>752000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>761000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>818000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>689000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>663000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>721000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>583000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>623000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>544000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>494000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>508000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>416000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>357000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>373000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>359000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>415000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>397000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>344000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>379000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>328000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>249000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>307000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>269000</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>4579000</v>
+      </c>
+      <c r="E42" s="3">
         <v>6660000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>5716000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>6798000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>4748000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>4529000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>4766000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>5482000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>4353000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>4682000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>5137000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>4488000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>3892000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>3243000</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -4435,130 +4524,136 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>12382000</v>
+      </c>
+      <c r="E43" s="3">
         <v>11423000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>10992000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>11621000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>12042000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>11575000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>11110000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>11271000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>11491000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>10829000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>10282000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>10345000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>10327000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>9483000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>9946000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>10085000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>10328000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>9859000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>8987000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>9373000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>9635000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>9332000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>8601000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>9127000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>9404000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>9232000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>8598000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>8979000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>8297000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>7947000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>7506000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>7639000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>7786000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>7536000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>7144000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>7267000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>7345000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>7012000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>6722000</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>6785000</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4601,8 +4696,8 @@
       <c r="P44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4679,53 +4774,56 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>11996000</v>
+      </c>
+      <c r="E45" s="3">
         <v>11840000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>16323000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>12172000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>11939000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>12001000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>11923000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>12032000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>12096000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>12014000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>12080000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>12357000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>12219000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>12283000</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -4801,53 +4899,56 @@
       <c r="AP45" s="3">
         <v>0</v>
       </c>
+      <c r="AQ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>29578000</v>
+      </c>
+      <c r="E46" s="3">
         <v>30538000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>33873000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>31320000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>29388000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>28829000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>28498000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>29557000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>28669000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>28192000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>28149000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>27783000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>27043000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>25776000</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4923,130 +5024,136 @@
       <c r="AP46" s="3">
         <v>0</v>
       </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>97716000</v>
+      </c>
+      <c r="E47" s="3">
         <v>95419000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>94566000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>95998000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>92426000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>90270000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>88555000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>89067000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>84202000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>83017000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>82714000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>77508000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>78128000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>77839000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>83081000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>80908000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>83224000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>86590000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>90286000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>90526000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>89546000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>87140000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>87639000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>86951000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>83953000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>80318000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>81540000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>81259000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>79307000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>78359000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>76159000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>75789000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>75037000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>75605000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>76345000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>76926000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>76111000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>74999000</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>74169000</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>76615000</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -5089,208 +5196,214 @@
       <c r="P48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="Q48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R48" s="3">
         <v>952000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>954000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>970000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>975000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>979000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1004000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1015000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1018000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1026000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>957000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>962000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>966000</v>
-      </c>
-      <c r="AC48" s="3">
-        <v>963000</v>
       </c>
       <c r="AD48" s="3">
         <v>963000</v>
       </c>
       <c r="AE48" s="3">
+        <v>963000</v>
+      </c>
+      <c r="AF48" s="3">
         <v>965000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>969000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>904000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>951000</v>
-      </c>
-      <c r="AI48" s="3">
-        <v>954000</v>
       </c>
       <c r="AJ48" s="3">
         <v>954000</v>
       </c>
       <c r="AK48" s="3">
+        <v>954000</v>
+      </c>
+      <c r="AL48" s="3">
         <v>932000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>923000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>920000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>926000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>928000</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>929000</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>8098000</v>
+      </c>
+      <c r="E49" s="3">
         <v>7978000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>7920000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>8304000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>8298000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>8141000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>8087000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>8220000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>8129000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>8007000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>7559000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>7563000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>7470000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>7249000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4239000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4209000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4261000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4302000</v>
-      </c>
-      <c r="U49" s="3">
-        <v>4314000</v>
       </c>
       <c r="V49" s="3">
         <v>4314000</v>
       </c>
       <c r="W49" s="3">
+        <v>4314000</v>
+      </c>
+      <c r="X49" s="3">
         <v>4334000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>4335000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>4293000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>4263000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>4244000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>4237000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>4291000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>4258000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>4278000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>4290000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>4282000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>4309000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>4287000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>4300000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>4293000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>4291000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>3853000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>3850000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>3848000</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>3856000</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5411,8 +5524,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5533,65 +5649,68 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>7147000</v>
+      </c>
+      <c r="E52" s="3">
         <v>7273000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>6462000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>7021000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>7131000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>7098000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>6287000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>6408000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>6527000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>6555000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>6052000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6137000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>6086000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>5920000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1877000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2175000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1374000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>662000</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V52" s="3" t="s">
         <v>8</v>
       </c>
@@ -5610,12 +5729,12 @@
       <c r="AA52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AB52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC52" s="3">
         <v>9000</v>
       </c>
-      <c r="AC52" s="3">
-        <v>0</v>
-      </c>
       <c r="AD52" s="3">
         <v>0</v>
       </c>
@@ -5623,40 +5742,43 @@
         <v>0</v>
       </c>
       <c r="AF52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG52" s="3">
         <v>115000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>445000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>521000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>463000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>368000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>70000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>243000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>201000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>261000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>465000</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5777,130 +5899,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>143580000</v>
+      </c>
+      <c r="E54" s="3">
         <v>142309000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>143708000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>143678000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>138873000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>135977000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>133189000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>134588000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>129315000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>127410000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>125978000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>121384000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>120573000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>118352000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>115717000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>114317000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>116587000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>118592000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>120466000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>120706000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>119759000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>117032000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>116764000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>116384000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>113337000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>109436000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>110122000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>110241000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>108572000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>107246000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>104233000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>104390000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>103523000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>103676000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>103483000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>104311000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>102669000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>101246000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>100245000</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>102787000</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5943,8 +6071,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5987,53 +6116,54 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>68242000</v>
+      </c>
+      <c r="E57" s="3">
         <v>68035000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>66346000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>68651000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>67928000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>67068000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>64724000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>65667000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>64726000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>63374000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>62222000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>62516000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>61297000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>59825000</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
-      </c>
       <c r="R57" s="3">
         <v>0</v>
       </c>
@@ -6109,25 +6239,28 @@
       <c r="AP57" s="3">
         <v>0</v>
       </c>
+      <c r="AQ57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>100000</v>
+      </c>
+      <c r="E58" s="3">
         <v>300000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>369000</v>
-      </c>
-      <c r="F58" s="3">
-        <v>300000</v>
       </c>
       <c r="G58" s="3">
         <v>300000</v>
       </c>
       <c r="H58" s="3">
-        <v>100000</v>
+        <v>300000</v>
       </c>
       <c r="I58" s="3">
         <v>100000</v>
@@ -6181,7 +6314,7 @@
         <v>100000</v>
       </c>
       <c r="Z58" s="3">
-        <v>600000</v>
+        <v>100000</v>
       </c>
       <c r="AA58" s="3">
         <v>600000</v>
@@ -6193,13 +6326,13 @@
         <v>600000</v>
       </c>
       <c r="AD58" s="3">
-        <v>100000</v>
+        <v>600000</v>
       </c>
       <c r="AE58" s="3">
         <v>100000</v>
       </c>
       <c r="AF58" s="3">
-        <v>600000</v>
+        <v>100000</v>
       </c>
       <c r="AG58" s="3">
         <v>600000</v>
@@ -6208,198 +6341,204 @@
         <v>600000</v>
       </c>
       <c r="AI58" s="3">
-        <v>500000</v>
+        <v>600000</v>
       </c>
       <c r="AJ58" s="3">
         <v>500000</v>
       </c>
       <c r="AK58" s="3">
+        <v>500000</v>
+      </c>
+      <c r="AL58" s="3">
         <v>600000</v>
-      </c>
-      <c r="AL58" s="3">
-        <v>950000</v>
       </c>
       <c r="AM58" s="3">
         <v>950000</v>
       </c>
       <c r="AN58" s="3">
-        <v>550000</v>
+        <v>950000</v>
       </c>
       <c r="AO58" s="3">
         <v>550000</v>
       </c>
       <c r="AP58" s="3">
+        <v>550000</v>
+      </c>
+      <c r="AQ58" s="3">
         <v>100000</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>23327000</v>
+      </c>
+      <c r="E59" s="3">
         <v>22772000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>26250000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>23596000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>23288000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>22724000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>23613000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>22783000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>22090000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>21307000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>21157000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>21058000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>20214000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>19143000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>80904000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>80898000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>80167000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>79379000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>77671000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>78146000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>76789000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>76074000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>74360000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>74883000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>73210000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>72186000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>71435000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>71899000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>70978000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>70286000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>69297000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>69714000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>68942000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>68567000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>67614000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>68177000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>66690000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>66231000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>65160000</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>65885000</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>91669000</v>
+      </c>
+      <c r="E60" s="3">
         <v>91107000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>92965000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>92547000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>91516000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>89892000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>88437000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>88550000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>86916000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>84781000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>83479000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>83674000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>81611000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>79068000</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6475,8 +6614,11 @@
       <c r="AP60" s="3">
         <v>0</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -6484,16 +6626,16 @@
         <v>8968000</v>
       </c>
       <c r="E61" s="3">
+        <v>8968000</v>
+      </c>
+      <c r="F61" s="3">
         <v>9143000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>8967000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>7734000</v>
-      </c>
-      <c r="H61" s="3">
-        <v>7933000</v>
       </c>
       <c r="I61" s="3">
         <v>7933000</v>
@@ -6502,13 +6644,13 @@
         <v>7933000</v>
       </c>
       <c r="K61" s="3">
-        <v>7932000</v>
+        <v>7933000</v>
       </c>
       <c r="L61" s="3">
         <v>7932000</v>
       </c>
       <c r="M61" s="3">
-        <v>7931000</v>
+        <v>7932000</v>
       </c>
       <c r="N61" s="3">
         <v>7931000</v>
@@ -6517,13 +6659,13 @@
         <v>7931000</v>
       </c>
       <c r="P61" s="3">
-        <v>7192000</v>
+        <v>7931000</v>
       </c>
       <c r="Q61" s="3">
         <v>7192000</v>
       </c>
       <c r="R61" s="3">
-        <v>7191000</v>
+        <v>7192000</v>
       </c>
       <c r="S61" s="3">
         <v>7191000</v>
@@ -6532,7 +6674,7 @@
         <v>7191000</v>
       </c>
       <c r="U61" s="3">
-        <v>7190000</v>
+        <v>7191000</v>
       </c>
       <c r="V61" s="3">
         <v>7190000</v>
@@ -6541,7 +6683,7 @@
         <v>7190000</v>
       </c>
       <c r="X61" s="3">
-        <v>6450000</v>
+        <v>7190000</v>
       </c>
       <c r="Y61" s="3">
         <v>6450000</v>
@@ -6550,25 +6692,25 @@
         <v>6450000</v>
       </c>
       <c r="AA61" s="3">
+        <v>6450000</v>
+      </c>
+      <c r="AB61" s="3">
         <v>6449000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>5959000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>5958000</v>
-      </c>
-      <c r="AD61" s="3">
-        <v>6458000</v>
       </c>
       <c r="AE61" s="3">
         <v>6458000</v>
       </c>
       <c r="AF61" s="3">
+        <v>6458000</v>
+      </c>
+      <c r="AG61" s="3">
         <v>6457000</v>
-      </c>
-      <c r="AG61" s="3">
-        <v>5964000</v>
       </c>
       <c r="AH61" s="3">
         <v>5964000</v>
@@ -6577,73 +6719,76 @@
         <v>5964000</v>
       </c>
       <c r="AJ61" s="3">
+        <v>5964000</v>
+      </c>
+      <c r="AK61" s="3">
         <v>6463000</v>
-      </c>
-      <c r="AK61" s="3">
-        <v>5971000</v>
       </c>
       <c r="AL61" s="3">
         <v>5971000</v>
       </c>
       <c r="AM61" s="3">
+        <v>5971000</v>
+      </c>
+      <c r="AN61" s="3">
         <v>5970000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>5888000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>5887000</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>6336000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>9822000</v>
+      </c>
+      <c r="E62" s="3">
         <v>10248000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>8706000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>10555000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>10105000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>9961000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>8955000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>10409000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>9605000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>9675000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>9647000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>9801000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>9176000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>9040000</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
-      </c>
       <c r="R62" s="3">
         <v>0</v>
       </c>
@@ -6654,41 +6799,41 @@
         <v>0</v>
       </c>
       <c r="U62" s="3">
+        <v>0</v>
+      </c>
+      <c r="V62" s="3">
         <v>289000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>274000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>415000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>293000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>558000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>448000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>409000</v>
       </c>
-      <c r="AB62" s="3">
-        <v>0</v>
-      </c>
       <c r="AC62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD62" s="3">
         <v>137000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>188000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>87000</v>
       </c>
-      <c r="AF62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG62" s="3" t="s">
         <v>8</v>
       </c>
@@ -6701,8 +6846,8 @@
       <c r="AJ62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK62" s="3">
-        <v>0</v>
+      <c r="AK62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AL62" s="3">
         <v>0</v>
@@ -6710,17 +6855,20 @@
       <c r="AM62" s="3">
         <v>0</v>
       </c>
-      <c r="AN62" s="3" t="s">
-        <v>8</v>
+      <c r="AN62" s="3">
+        <v>0</v>
       </c>
       <c r="AO62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AP62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AQ62" s="3">
         <v>171000</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6841,8 +6989,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6963,8 +7114,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7085,130 +7239,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>110459000</v>
+      </c>
+      <c r="E66" s="3">
         <v>110323000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>110814000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>112069000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>109355000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>107786000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>105325000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>106892000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>104453000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>102388000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>101057000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>101406000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>98718000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>95300000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>94157000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>94411000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>93713000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>93061000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>91579000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>92232000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>90603000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>88763000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>87563000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>88535000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>86394000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>84232000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>84179000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>84634000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>83251000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>82906000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>81339000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>81930000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>80900000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>80697000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>79752000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>80573000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>78811000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>77634000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>77024000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>78348000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7251,8 +7411,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7373,8 +7534,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7495,8 +7659,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7617,8 +7784,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7739,130 +7909,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>58346000</v>
+      </c>
+      <c r="E72" s="3">
         <v>56404000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>54931000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>52680000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>51041000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>49784000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>49630000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>47789000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>46773000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>46483000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>45591000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>44198000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>44026000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>44273000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>43516000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>42917000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>42684000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>42359000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>41555000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>40438000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>39998000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>39285000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>38771000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>37679000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>37069000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>37325000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>36977000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>36317000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>36135000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>35795000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>35204000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>34799000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>34296000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>33981000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>33462000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>33110000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>33016000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>32623000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>32196000</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>31443000</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7983,8 +8159,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8105,8 +8284,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8227,130 +8409,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>33121000</v>
+      </c>
+      <c r="E76" s="3">
         <v>31986000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>32894000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>31609000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>29518000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>28191000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>27864000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>27696000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>24862000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>25022000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>24921000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>19978000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>21855000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>23052000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>21560000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>19906000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>22874000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>25531000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>28887000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>28474000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>29156000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>28269000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>29201000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>27849000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>26943000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>25204000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>25943000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>25607000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>25321000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>24340000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>22894000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>22460000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>22623000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>22979000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>23731000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>23738000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>23858000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>23612000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>23221000</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>24439000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8471,257 +8659,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2208000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1711000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2496000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1888000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1509000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>395000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2082000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1260000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>534000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1123000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1626000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>404000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-14000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>975000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>814000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>450000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>547000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1011000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1323000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>657000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>927000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>728000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1300000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>821000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-41000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>595000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>866000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>393000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>553000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>791000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>616000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>704000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>520000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>664000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>547000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>291000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>590000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>613000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>937000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>710000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8764,130 +8961,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>164000</v>
+      </c>
+      <c r="E83" s="3">
         <v>188000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>142000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>174000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>182000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>196000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>158000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>169000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>179000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>204000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>174000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>195000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>210000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>234000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1621000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1601000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1575000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1544000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1509000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1493000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1469000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>1442000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>1427000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>1393000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>1361000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>1381000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>1363000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>1349000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>1324000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>1328000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>1316000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>1315000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>1280000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>1273000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>1274000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>1261000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>1230000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>1214000</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>1215000</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>1223000</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9008,8 +9209,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9130,8 +9334,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9252,8 +9459,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9374,8 +9584,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9496,130 +9709,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1916000</v>
+      </c>
+      <c r="E89" s="3">
         <v>2198000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2685000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>4227000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2334000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1360000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2064000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3875000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1677000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1458000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2104000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3046000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1549000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1012000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1340000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>2484000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1375000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1266000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1692000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>2543000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1849000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1190000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1901000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>2326000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1664000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>628000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1412000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>2001000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1153000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>639000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>948000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1734000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1144000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>554000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>663000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>1731000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>906000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>848000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>1139000</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>1770000</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9662,8 +9881,9 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -9706,8 +9926,8 @@
       <c r="P91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
+      <c r="Q91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
@@ -9784,8 +10004,11 @@
       <c r="AP91" s="3">
         <v>0</v>
       </c>
+      <c r="AQ91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9906,8 +10129,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10028,130 +10254,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-165000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-335000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-575000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-4553000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1716000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-808000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1693000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3391000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1143000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1037000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1784000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2725000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1857000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-455000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-674000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1687000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-710000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-657000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-774000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1637000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-2011000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-774000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-915000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2163000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1898000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>84000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-855000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1346000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-115000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-586000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-570000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1302000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-76000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-381000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>299000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-1094000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-579000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-442000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-326000</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-1043000</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10194,130 +10426,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>263000</v>
+      </c>
+      <c r="E96" s="3">
         <v>237000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>242000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>247000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>250000</v>
-      </c>
-      <c r="H96" s="3">
-        <v>240000</v>
       </c>
       <c r="I96" s="3">
         <v>240000</v>
       </c>
       <c r="J96" s="3">
+        <v>240000</v>
+      </c>
+      <c r="K96" s="3">
         <v>238000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>244000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>229000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>232000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>229000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>232000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>215000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-219000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-220000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-223000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-213000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-214000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-219000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-222000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-214000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-218000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-217000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-216000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-210000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-211000</v>
-      </c>
-      <c r="AD96" s="3">
-        <v>-214000</v>
       </c>
       <c r="AE96" s="3">
         <v>-214000</v>
       </c>
       <c r="AF96" s="3">
+        <v>-214000</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-205000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-203000</v>
-      </c>
-      <c r="AH96" s="3">
-        <v>-207000</v>
       </c>
       <c r="AI96" s="3">
         <v>-207000</v>
       </c>
       <c r="AJ96" s="3">
+        <v>-207000</v>
+      </c>
+      <c r="AK96" s="3">
         <v>-197000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-196000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-200000</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-199000</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-190000</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-188000</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-194000</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10438,8 +10674,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10560,8 +10799,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10682,370 +10924,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1743000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2085000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1828000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>402000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-702000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-535000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-422000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-454000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-472000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-399000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-273000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-323000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>138000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-593000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-658000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-710000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-688000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-613000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-978000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-770000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>188000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-477000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-864000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-210000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>308000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-650000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-580000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-557000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-979000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-71000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-358000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-488000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-1044000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-122000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-872000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-498000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-157000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-393000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-771000</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-721000</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E101" s="3">
         <v>8000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-22000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>13000</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>-5000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>10000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-10000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>8000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>4000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>18000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-24000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-19000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>18000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-24000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-19000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-5000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>3000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-7000</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
       <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
         <v>3000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>16000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>7000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>5000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-12000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>9000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-6000</v>
       </c>
-      <c r="AE101" s="3">
-        <v>0</v>
-      </c>
       <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="3">
         <v>2000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-6000</v>
       </c>
-      <c r="AH101" s="3">
-        <v>0</v>
-      </c>
       <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ101" s="3">
         <v>-6000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>2000</v>
       </c>
-      <c r="AK101" s="3">
-        <v>0</v>
-      </c>
       <c r="AL101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM101" s="3">
         <v>4000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>5000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>2000</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-4000</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-227000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>284000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>70000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-65000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>25000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-73000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>43000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>62000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>17000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>57000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-12000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-162000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-32000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>26000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>63000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-42000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-9000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-57000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>129000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>26000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-58000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>138000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-40000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>79000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>50000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-14000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>92000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>59000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-16000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>14000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-56000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>18000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>53000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-35000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>51000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>79000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-58000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>38000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>4000</v>
       </c>
     </row>
